--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$and）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$and）.xlsx
@@ -76,23 +76,25 @@
     <t>使用$and查询，指定多个不同数据类型的值</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，$and指定多个值，且为不同类型的值
-2、检查查询结果正确性</t>
-  </si>
-  <si>
     <t>使用$and查询，给定值为空（如{$and:[]}）</t>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，$and指定值为空，如{$and:[]}
-2、检查查询结果正确性</t>
-  </si>
-  <si>
-    <t>1、find{$and:[{&lt;表达式1&gt;}，{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]}查询，目标字段覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
+    <t>1、find({$and:[{&lt;表达式1&gt;}，{&lt;表达式2&gt;},...,{&lt;表达式N&gt;}]})查询，目标字段覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
 2、检查查询结果正确性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，目标字段为索引字段，且目标字段需要覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
+    <t>1、find({&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，目标字段为索引字段，且目标字段需要覆盖所有数据类型（覆盖多层嵌套数组），取值个数覆盖：1个、多个
+2、检查查询结果正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$and指定多个值，且为不同类型的值
+2、检查查询结果正确性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$and:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$and指定值为空，如{$and:[]}
 2、检查查询结果正确性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -625,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -651,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
@@ -678,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
@@ -689,7 +691,7 @@
     </row>
     <row r="5" spans="1:9" ht="40.5">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -704,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
